--- a/xls/square_high_un_16_tri3_9.xlsx
+++ b/xls/square_high_un_16_tri3_9.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>122</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>340</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>336</v>
+      </c>
+      <c r="I7">
+        <v>23.759249169644793</v>
+      </c>
+      <c r="J7">
+        <v>10.058988221974243</v>
+      </c>
+      <c r="K7">
+        <v>8.831992140805337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>340</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>480</v>
+      </c>
+      <c r="I8">
+        <v>-0.5451888537943975</v>
+      </c>
+      <c r="J8">
+        <v>-0.9859909852483031</v>
+      </c>
+      <c r="K8">
+        <v>-0.3807367991540102</v>
+      </c>
+    </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
